--- a/ExcelTool/LubanTools/DataTables/Datas/DialogueData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/DialogueData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D066A4EF-4808-47E3-8CE3-32E427AABDB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F803805-615D-4A21-AB0B-35749F3B643F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-2520" yWindow="3150" windowWidth="41500" windowHeight="15380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -399,7 +399,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -421,6 +421,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,7 +482,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -496,12 +502,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -518,6 +518,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -832,34 +841,34 @@
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="8" t="s">
+      <c r="B1" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="7" t="s">
         <v>5</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="15" t="s">
         <v>7</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="15" t="s">
         <v>12</v>
       </c>
       <c r="L1" s="5" t="s">
@@ -871,13 +880,13 @@
       <c r="N1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="O1" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="P1" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="Q1" s="15" t="s">
         <v>18</v>
       </c>
       <c r="R1" s="5" t="s">
@@ -917,37 +926,37 @@
       <c r="C2" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="J2" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="K2" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="L2" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="M2" s="9" t="s">
+      <c r="M2" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="N2" s="13" t="s">
+      <c r="N2" s="11" t="s">
         <v>66</v>
       </c>
       <c r="O2" s="5" t="s">
@@ -959,13 +968,13 @@
       <c r="Q2" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="R2" s="10" t="s">
+      <c r="R2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="S2" s="10" t="s">
+      <c r="S2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="T2" s="10" t="s">
+      <c r="T2" s="8" t="s">
         <v>25</v>
       </c>
       <c r="U2" s="5" t="s">
@@ -996,7 +1005,7 @@
       <c r="C3" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="7" t="s">
         <v>29</v>
       </c>
       <c r="E3" s="5" t="s">
@@ -1081,7 +1090,7 @@
       <c r="F4" s="5">
         <v>-1</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="9" t="s">
         <v>63</v>
       </c>
       <c r="H4" s="3" t="s">
@@ -1091,7 +1100,7 @@
         <v>10001</v>
       </c>
       <c r="K4" s="1"/>
-      <c r="N4" s="12" t="s">
+      <c r="N4" s="10" t="s">
         <v>65</v>
       </c>
       <c r="O4" s="1" t="b">
@@ -1109,7 +1118,7 @@
       <c r="V4" s="1">
         <v>3</v>
       </c>
-      <c r="W4" s="14" t="s">
+      <c r="W4" s="12" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1129,7 +1138,7 @@
       <c r="F5" s="5">
         <v>-1</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="9" t="s">
         <v>63</v>
       </c>
       <c r="H5" s="3" t="s">
@@ -1141,7 +1150,7 @@
       <c r="K5" s="1">
         <v>10000</v>
       </c>
-      <c r="N5" s="12" t="s">
+      <c r="N5" s="10" t="s">
         <v>65</v>
       </c>
       <c r="O5" s="1" t="b">
@@ -1159,7 +1168,7 @@
       <c r="V5" s="1">
         <v>1</v>
       </c>
-      <c r="W5" s="14" t="s">
+      <c r="W5" s="12" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1179,7 +1188,7 @@
       <c r="F6" s="5">
         <v>10000</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="9" t="s">
         <v>63</v>
       </c>
       <c r="H6" s="3" t="s">
@@ -1191,7 +1200,7 @@
       <c r="K6" s="1">
         <v>10001</v>
       </c>
-      <c r="N6" s="12" t="s">
+      <c r="N6" s="10" t="s">
         <v>65</v>
       </c>
       <c r="O6" s="1" t="b">
@@ -1209,7 +1218,7 @@
       <c r="V6" s="1">
         <v>3</v>
       </c>
-      <c r="W6" s="14" t="s">
+      <c r="W6" s="12" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1229,7 +1238,7 @@
       <c r="F7" s="5">
         <v>10000</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="9" t="s">
         <v>63</v>
       </c>
       <c r="H7" s="3" t="s">
@@ -1241,7 +1250,7 @@
       <c r="K7" s="1">
         <v>10002</v>
       </c>
-      <c r="N7" s="12" t="s">
+      <c r="N7" s="10" t="s">
         <v>65</v>
       </c>
       <c r="O7" s="1" t="b">
@@ -1259,7 +1268,7 @@
       <c r="V7" s="1">
         <v>1</v>
       </c>
-      <c r="W7" s="14" t="s">
+      <c r="W7" s="12" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1279,7 +1288,7 @@
       <c r="F8" s="5">
         <v>10001</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="9" t="s">
         <v>63</v>
       </c>
       <c r="H8" s="4" t="s">
@@ -1289,7 +1298,7 @@
         <v>10101</v>
       </c>
       <c r="K8" s="2"/>
-      <c r="N8" s="12" t="s">
+      <c r="N8" s="10" t="s">
         <v>65</v>
       </c>
       <c r="O8" s="2" t="b">
@@ -1307,7 +1316,7 @@
       <c r="V8" s="2">
         <v>3</v>
       </c>
-      <c r="W8" s="14" t="s">
+      <c r="W8" s="12" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1327,7 +1336,7 @@
       <c r="F9" s="5">
         <v>10001</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="9" t="s">
         <v>63</v>
       </c>
       <c r="H9" s="4" t="s">
@@ -1339,7 +1348,7 @@
       <c r="K9" s="2">
         <v>10100</v>
       </c>
-      <c r="N9" s="12" t="s">
+      <c r="N9" s="10" t="s">
         <v>65</v>
       </c>
       <c r="O9" s="2" t="b">
@@ -1357,7 +1366,7 @@
       <c r="V9" s="2">
         <v>1</v>
       </c>
-      <c r="W9" s="14" t="s">
+      <c r="W9" s="12" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1377,7 +1386,7 @@
       <c r="F10" s="5">
         <v>10001</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="9" t="s">
         <v>63</v>
       </c>
       <c r="H10" s="4" t="s">
@@ -1389,7 +1398,7 @@
       <c r="K10" s="2">
         <v>10101</v>
       </c>
-      <c r="N10" s="12" t="s">
+      <c r="N10" s="10" t="s">
         <v>65</v>
       </c>
       <c r="O10" s="2" t="b">
@@ -1407,7 +1416,7 @@
       <c r="V10" s="2">
         <v>3</v>
       </c>
-      <c r="W10" s="14" t="s">
+      <c r="W10" s="12" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1427,7 +1436,7 @@
       <c r="F11" s="5">
         <v>10001</v>
       </c>
-      <c r="G11" s="11" t="s">
+      <c r="G11" s="9" t="s">
         <v>63</v>
       </c>
       <c r="H11" s="4" t="s">
@@ -1442,7 +1451,7 @@
       <c r="K11" s="2">
         <v>10102</v>
       </c>
-      <c r="N11" s="12" t="s">
+      <c r="N11" s="10" t="s">
         <v>65</v>
       </c>
       <c r="O11" s="2" t="b">
@@ -1460,7 +1469,7 @@
       <c r="V11" s="2">
         <v>3</v>
       </c>
-      <c r="W11" s="14" t="s">
+      <c r="W11" s="12" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1480,7 +1489,7 @@
       <c r="F12" s="5">
         <v>10001</v>
       </c>
-      <c r="G12" s="11" t="s">
+      <c r="G12" s="9" t="s">
         <v>63</v>
       </c>
       <c r="H12" s="2" t="s">
@@ -1490,7 +1499,7 @@
         <v>10105</v>
       </c>
       <c r="K12" s="2"/>
-      <c r="N12" s="12" t="s">
+      <c r="N12" s="10" t="s">
         <v>65</v>
       </c>
       <c r="O12" s="2" t="b">
@@ -1508,7 +1517,7 @@
       <c r="V12" s="2">
         <v>3</v>
       </c>
-      <c r="W12" s="14" t="s">
+      <c r="W12" s="12" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1528,7 +1537,7 @@
       <c r="F13" s="5">
         <v>10001</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="G13" s="9" t="s">
         <v>63</v>
       </c>
       <c r="H13" s="2" t="s">
@@ -1538,7 +1547,7 @@
         <v>-1</v>
       </c>
       <c r="K13" s="2"/>
-      <c r="N13" s="12" t="s">
+      <c r="N13" s="10" t="s">
         <v>65</v>
       </c>
       <c r="O13" s="2" t="b">
@@ -1556,7 +1565,7 @@
       <c r="V13" s="2">
         <v>3</v>
       </c>
-      <c r="W13" s="14" t="s">
+      <c r="W13" s="12" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1576,7 +1585,7 @@
       <c r="F14" s="5">
         <v>10001</v>
       </c>
-      <c r="G14" s="11" t="s">
+      <c r="G14" s="9" t="s">
         <v>63</v>
       </c>
       <c r="H14" s="2" t="s">
@@ -1586,7 +1595,7 @@
         <v>10107</v>
       </c>
       <c r="K14" s="2"/>
-      <c r="N14" s="12" t="s">
+      <c r="N14" s="10" t="s">
         <v>65</v>
       </c>
       <c r="O14" s="2" t="b">
@@ -1604,7 +1613,7 @@
       <c r="V14" s="2">
         <v>3</v>
       </c>
-      <c r="W14" s="14" t="s">
+      <c r="W14" s="12" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1624,7 +1633,7 @@
       <c r="F15" s="5">
         <v>10001</v>
       </c>
-      <c r="G15" s="11" t="s">
+      <c r="G15" s="9" t="s">
         <v>63</v>
       </c>
       <c r="H15" s="2" t="s">
@@ -1634,7 +1643,7 @@
         <v>-1</v>
       </c>
       <c r="K15" s="2"/>
-      <c r="N15" s="12" t="s">
+      <c r="N15" s="10" t="s">
         <v>65</v>
       </c>
       <c r="O15" s="2" t="b">
@@ -1652,7 +1661,7 @@
       <c r="V15" s="2">
         <v>3</v>
       </c>
-      <c r="W15" s="14" t="s">
+      <c r="W15" s="12" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1672,7 +1681,7 @@
       <c r="F16" s="5">
         <v>10001</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="G16" s="9" t="s">
         <v>63</v>
       </c>
       <c r="H16" s="2" t="s">
@@ -1682,7 +1691,7 @@
         <v>10109</v>
       </c>
       <c r="K16" s="2"/>
-      <c r="N16" s="12" t="s">
+      <c r="N16" s="10" t="s">
         <v>65</v>
       </c>
       <c r="O16" s="2" t="b">
@@ -1700,7 +1709,7 @@
       <c r="V16" s="2">
         <v>3</v>
       </c>
-      <c r="W16" s="14" t="s">
+      <c r="W16" s="12" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1720,7 +1729,7 @@
       <c r="F17" s="5">
         <v>10002</v>
       </c>
-      <c r="G17" s="11" t="s">
+      <c r="G17" s="9" t="s">
         <v>63</v>
       </c>
       <c r="H17" s="2" t="s">
@@ -1730,7 +1739,7 @@
         <v>-1</v>
       </c>
       <c r="K17" s="2"/>
-      <c r="N17" s="12" t="s">
+      <c r="N17" s="10" t="s">
         <v>65</v>
       </c>
       <c r="O17" s="2" t="b">
@@ -1748,7 +1757,7 @@
       <c r="V17" s="2">
         <v>3</v>
       </c>
-      <c r="W17" s="14" t="s">
+      <c r="W17" s="12" t="s">
         <v>68</v>
       </c>
     </row>

--- a/ExcelTool/LubanTools/DataTables/Datas/DialogueData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/DialogueData.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F803805-615D-4A21-AB0B-35749F3B643F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-3230" yWindow="5240" windowWidth="38610" windowHeight="15380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1764,5 +1764,6 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/DialogueData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/DialogueData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F803805-615D-4A21-AB0B-35749F3B643F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{736091CA-6638-4AEE-B884-667DBE70FDCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-3230" yWindow="5240" windowWidth="38610" windowHeight="15380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-800" yWindow="4880" windowWidth="38610" windowHeight="16000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,8 +35,41 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={9638FB6C-ABC7-4DEB-BA79-91F240B16515}</author>
+    <author>tc={0F5F2D1B-07B1-4778-98B7-6F665943CEF5}</author>
+  </authors>
+  <commentList>
+    <comment ref="V2" authorId="0" shapeId="0" xr:uid="{9638FB6C-ABC7-4DEB-BA79-91F240B16515}">
+      <text>
+        <t xml:space="preserve">[线程批注]
+你的Excel版本可读取此线程批注; 但如果在更新版本的Excel中打开文件，则对批注所作的任何改动都将被删除。了解详细信息: https://go.microsoft.com/fwlink/?linkid=870924
+注释:
+    Left	左
+Crent	中
+Right	右
+</t>
+      </text>
+    </comment>
+    <comment ref="W2" authorId="1" shapeId="0" xr:uid="{0F5F2D1B-07B1-4778-98B7-6F665943CEF5}">
+      <text>
+        <t xml:space="preserve">[线程批注]
+你的Excel版本可读取此线程批注; 但如果在更新版本的Excel中打开文件，则对批注所作的任何改动都将被删除。了解详细信息: https://go.microsoft.com/fwlink/?linkid=870924
+注释:
+    DEL	删除
+MASK	遮罩
+OVERRIDE	同时展示
+</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="91">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -329,6 +362,18 @@
   </si>
   <si>
     <t>DramaDialogue+MaJi10109</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LlustrationDirection</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>右</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>左</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -336,7 +381,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -398,8 +443,15 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -427,6 +479,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,7 +540,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -529,6 +587,9 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -544,6 +605,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="ZhenYu Li" id="{AECE6D32-4610-4C2D-A4AA-6A736A2118FB}" userId="22722615eca45519" providerId="Windows Live"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -807,8 +874,25 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="V2" dT="2026-06-27T01:41:32.05" personId="{AECE6D32-4610-4C2D-A4AA-6A736A2118FB}" id="{9638FB6C-ABC7-4DEB-BA79-91F240B16515}">
+    <text xml:space="preserve">Left	左
+Crent	中
+Right	右
+</text>
+  </threadedComment>
+  <threadedComment ref="W2" dT="2026-06-27T01:41:47.97" personId="{AECE6D32-4610-4C2D-A4AA-6A736A2118FB}" id="{0F5F2D1B-07B1-4778-98B7-6F665943CEF5}">
+    <text xml:space="preserve">DEL	删除
+MASK	遮罩
+OVERRIDE	同时展示
+</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AE17"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
@@ -980,8 +1064,8 @@
       <c r="U2" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="V2" s="5" t="s">
-        <v>62</v>
+      <c r="V2" s="16" t="s">
+        <v>88</v>
       </c>
       <c r="W2" s="5" t="s">
         <v>67</v>
@@ -1115,8 +1199,8 @@
       <c r="U4" s="1">
         <v>1</v>
       </c>
-      <c r="V4" s="1">
-        <v>3</v>
+      <c r="V4" s="16" t="s">
+        <v>89</v>
       </c>
       <c r="W4" s="12" t="s">
         <v>68</v>
@@ -1165,8 +1249,8 @@
       <c r="U5" s="1">
         <v>1</v>
       </c>
-      <c r="V5" s="1">
-        <v>1</v>
+      <c r="V5" s="16" t="s">
+        <v>90</v>
       </c>
       <c r="W5" s="12" t="s">
         <v>68</v>
@@ -1215,8 +1299,8 @@
       <c r="U6" s="1">
         <v>1</v>
       </c>
-      <c r="V6" s="1">
-        <v>3</v>
+      <c r="V6" s="16" t="s">
+        <v>89</v>
       </c>
       <c r="W6" s="12" t="s">
         <v>68</v>
@@ -1265,8 +1349,8 @@
       <c r="U7" s="1">
         <v>1</v>
       </c>
-      <c r="V7" s="1">
-        <v>1</v>
+      <c r="V7" s="16" t="s">
+        <v>90</v>
       </c>
       <c r="W7" s="12" t="s">
         <v>68</v>
@@ -1313,8 +1397,8 @@
       <c r="U8" s="2">
         <v>1</v>
       </c>
-      <c r="V8" s="2">
-        <v>3</v>
+      <c r="V8" s="16" t="s">
+        <v>89</v>
       </c>
       <c r="W8" s="12" t="s">
         <v>68</v>
@@ -1363,8 +1447,8 @@
       <c r="U9" s="2">
         <v>1</v>
       </c>
-      <c r="V9" s="2">
-        <v>1</v>
+      <c r="V9" s="16" t="s">
+        <v>90</v>
       </c>
       <c r="W9" s="12" t="s">
         <v>68</v>
@@ -1413,8 +1497,8 @@
       <c r="U10" s="2">
         <v>1</v>
       </c>
-      <c r="V10" s="2">
-        <v>3</v>
+      <c r="V10" s="16" t="s">
+        <v>89</v>
       </c>
       <c r="W10" s="12" t="s">
         <v>68</v>
@@ -1466,8 +1550,8 @@
       <c r="U11" s="2">
         <v>1</v>
       </c>
-      <c r="V11" s="2">
-        <v>3</v>
+      <c r="V11" s="16" t="s">
+        <v>89</v>
       </c>
       <c r="W11" s="12" t="s">
         <v>68</v>
@@ -1514,8 +1598,8 @@
       <c r="U12" s="2">
         <v>1</v>
       </c>
-      <c r="V12" s="2">
-        <v>3</v>
+      <c r="V12" s="16" t="s">
+        <v>89</v>
       </c>
       <c r="W12" s="12" t="s">
         <v>68</v>
@@ -1562,8 +1646,8 @@
       <c r="U13" s="2">
         <v>1</v>
       </c>
-      <c r="V13" s="2">
-        <v>3</v>
+      <c r="V13" s="16" t="s">
+        <v>89</v>
       </c>
       <c r="W13" s="12" t="s">
         <v>68</v>
@@ -1610,8 +1694,8 @@
       <c r="U14" s="2">
         <v>1</v>
       </c>
-      <c r="V14" s="2">
-        <v>3</v>
+      <c r="V14" s="16" t="s">
+        <v>89</v>
       </c>
       <c r="W14" s="12" t="s">
         <v>68</v>
@@ -1658,8 +1742,8 @@
       <c r="U15" s="2">
         <v>1</v>
       </c>
-      <c r="V15" s="2">
-        <v>3</v>
+      <c r="V15" s="16" t="s">
+        <v>89</v>
       </c>
       <c r="W15" s="12" t="s">
         <v>68</v>
@@ -1706,8 +1790,8 @@
       <c r="U16" s="2">
         <v>1</v>
       </c>
-      <c r="V16" s="2">
-        <v>3</v>
+      <c r="V16" s="16" t="s">
+        <v>89</v>
       </c>
       <c r="W16" s="12" t="s">
         <v>68</v>
@@ -1754,8 +1838,8 @@
       <c r="U17" s="2">
         <v>1</v>
       </c>
-      <c r="V17" s="2">
-        <v>3</v>
+      <c r="V17" s="16" t="s">
+        <v>89</v>
       </c>
       <c r="W17" s="12" t="s">
         <v>68</v>
@@ -1765,5 +1849,6 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/DialogueData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/DialogueData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{736091CA-6638-4AEE-B884-667DBE70FDCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F1D860B-1E91-4809-BF19-1F511476EBDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-800" yWindow="4880" windowWidth="38610" windowHeight="16000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3380" yWindow="3910" windowWidth="38610" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="95">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -374,6 +374,22 @@
   </si>
   <si>
     <t>左</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActionType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对话结束后事件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DialogueEndActionType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Node</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -381,7 +397,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -439,13 +455,6 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -540,7 +549,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -588,6 +597,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -918,7 +930,8 @@
     <col min="21" max="21" width="17.08203125" style="6" customWidth="1"/>
     <col min="22" max="22" width="20" style="6" customWidth="1"/>
     <col min="23" max="23" width="25.9140625" style="6" customWidth="1"/>
-    <col min="24" max="16384" width="8.6640625" style="6"/>
+    <col min="24" max="24" width="22.58203125" style="6" customWidth="1"/>
+    <col min="25" max="16384" width="8.6640625" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="15.5" x14ac:dyDescent="0.3">
@@ -991,7 +1004,9 @@
       <c r="W1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="X1" s="5"/>
+      <c r="X1" s="5" t="s">
+        <v>91</v>
+      </c>
       <c r="Y1" s="5"/>
       <c r="Z1" s="5"/>
       <c r="AA1" s="5"/>
@@ -1070,7 +1085,9 @@
       <c r="W2" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="X2" s="5"/>
+      <c r="X2" s="17" t="s">
+        <v>93</v>
+      </c>
       <c r="Y2" s="5"/>
       <c r="Z2" s="5"/>
       <c r="AA2" s="5"/>
@@ -1149,7 +1166,9 @@
       <c r="W3" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="X3" s="5"/>
+      <c r="X3" s="5" t="s">
+        <v>92</v>
+      </c>
       <c r="Y3" s="5"/>
       <c r="Z3" s="5"/>
       <c r="AA3" s="5"/>
@@ -1205,6 +1224,9 @@
       <c r="W4" s="12" t="s">
         <v>68</v>
       </c>
+      <c r="X4" s="17" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B5" s="1">
@@ -1255,6 +1277,9 @@
       <c r="W5" s="12" t="s">
         <v>68</v>
       </c>
+      <c r="X5" s="17" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B6" s="1">
@@ -1305,6 +1330,9 @@
       <c r="W6" s="12" t="s">
         <v>68</v>
       </c>
+      <c r="X6" s="17" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B7" s="1">
@@ -1355,6 +1383,9 @@
       <c r="W7" s="12" t="s">
         <v>68</v>
       </c>
+      <c r="X7" s="17" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
@@ -1403,6 +1434,9 @@
       <c r="W8" s="12" t="s">
         <v>68</v>
       </c>
+      <c r="X8" s="17" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B9" s="2">
@@ -1453,6 +1487,9 @@
       <c r="W9" s="12" t="s">
         <v>68</v>
       </c>
+      <c r="X9" s="17" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B10" s="2">
@@ -1503,6 +1540,9 @@
       <c r="W10" s="12" t="s">
         <v>68</v>
       </c>
+      <c r="X10" s="17" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B11" s="2">
@@ -1556,6 +1596,9 @@
       <c r="W11" s="12" t="s">
         <v>68</v>
       </c>
+      <c r="X11" s="17" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B12" s="2">
@@ -1604,6 +1647,9 @@
       <c r="W12" s="12" t="s">
         <v>68</v>
       </c>
+      <c r="X12" s="17" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B13" s="2">
@@ -1652,6 +1698,9 @@
       <c r="W13" s="12" t="s">
         <v>68</v>
       </c>
+      <c r="X13" s="17" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B14" s="2">
@@ -1700,6 +1749,9 @@
       <c r="W14" s="12" t="s">
         <v>68</v>
       </c>
+      <c r="X14" s="17" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B15" s="2">
@@ -1748,6 +1800,9 @@
       <c r="W15" s="12" t="s">
         <v>68</v>
       </c>
+      <c r="X15" s="17" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.3">
       <c r="B16" s="2">
@@ -1796,8 +1851,11 @@
       <c r="W16" s="12" t="s">
         <v>68</v>
       </c>
+      <c r="X16" s="17" t="s">
+        <v>94</v>
+      </c>
     </row>
-    <row r="17" spans="2:23" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:24" x14ac:dyDescent="0.3">
       <c r="B17" s="2">
         <v>10109</v>
       </c>
@@ -1843,6 +1901,9 @@
       </c>
       <c r="W17" s="12" t="s">
         <v>68</v>
+      </c>
+      <c r="X17" s="17" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/DialogueData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/DialogueData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F1D860B-1E91-4809-BF19-1F511476EBDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CDA20FB-DC4B-4233-8DDE-4A91EAB0CF73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3380" yWindow="3910" windowWidth="38610" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-5010" yWindow="5830" windowWidth="38610" windowHeight="15710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="91">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -374,22 +374,6 @@
   </si>
   <si>
     <t>左</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ActionType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>对话结束后事件</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DialogueEndActionType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Node</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -549,7 +533,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -597,9 +581,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -905,7 +886,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AE17"/>
+  <dimension ref="A1:AD17"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="8.6640625" style="6"/>
@@ -930,11 +911,10 @@
     <col min="21" max="21" width="17.08203125" style="6" customWidth="1"/>
     <col min="22" max="22" width="20" style="6" customWidth="1"/>
     <col min="23" max="23" width="25.9140625" style="6" customWidth="1"/>
-    <col min="24" max="24" width="22.58203125" style="6" customWidth="1"/>
-    <col min="25" max="16384" width="8.6640625" style="6"/>
+    <col min="24" max="16384" width="8.6640625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="15.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" ht="15.5" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1004,18 +984,15 @@
       <c r="W1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="X1" s="5" t="s">
-        <v>91</v>
-      </c>
+      <c r="X1" s="5"/>
       <c r="Y1" s="5"/>
       <c r="Z1" s="5"/>
       <c r="AA1" s="5"/>
       <c r="AB1" s="5"/>
       <c r="AC1" s="5"/>
       <c r="AD1" s="5"/>
-      <c r="AE1" s="5"/>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
@@ -1085,18 +1062,15 @@
       <c r="W2" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="X2" s="17" t="s">
-        <v>93</v>
-      </c>
+      <c r="X2" s="5"/>
       <c r="Y2" s="5"/>
       <c r="Z2" s="5"/>
       <c r="AA2" s="5"/>
       <c r="AB2" s="5"/>
       <c r="AC2" s="5"/>
       <c r="AD2" s="5"/>
-      <c r="AE2" s="5"/>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
@@ -1166,18 +1140,15 @@
       <c r="W3" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="X3" s="5" t="s">
-        <v>92</v>
-      </c>
+      <c r="X3" s="5"/>
       <c r="Y3" s="5"/>
       <c r="Z3" s="5"/>
       <c r="AA3" s="5"/>
       <c r="AB3" s="5"/>
       <c r="AC3" s="5"/>
       <c r="AD3" s="5"/>
-      <c r="AE3" s="5"/>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B4" s="1">
         <v>10000</v>
       </c>
@@ -1224,11 +1195,8 @@
       <c r="W4" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="X4" s="17" t="s">
-        <v>94</v>
-      </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B5" s="1">
         <v>10001</v>
       </c>
@@ -1277,11 +1245,8 @@
       <c r="W5" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="X5" s="17" t="s">
-        <v>94</v>
-      </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B6" s="1">
         <v>10002</v>
       </c>
@@ -1330,11 +1295,8 @@
       <c r="W6" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="X6" s="17" t="s">
-        <v>94</v>
-      </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B7" s="1">
         <v>10003</v>
       </c>
@@ -1383,11 +1345,8 @@
       <c r="W7" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="X7" s="17" t="s">
-        <v>94</v>
-      </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
         <v>10100</v>
       </c>
@@ -1434,11 +1393,8 @@
       <c r="W8" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="X8" s="17" t="s">
-        <v>94</v>
-      </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B9" s="2">
         <v>10101</v>
       </c>
@@ -1487,11 +1443,8 @@
       <c r="W9" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="X9" s="17" t="s">
-        <v>94</v>
-      </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B10" s="2">
         <v>10102</v>
       </c>
@@ -1540,11 +1493,8 @@
       <c r="W10" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="X10" s="17" t="s">
-        <v>94</v>
-      </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B11" s="2">
         <v>10103</v>
       </c>
@@ -1596,11 +1546,8 @@
       <c r="W11" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="X11" s="17" t="s">
-        <v>94</v>
-      </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B12" s="2">
         <v>10104</v>
       </c>
@@ -1647,11 +1594,8 @@
       <c r="W12" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="X12" s="17" t="s">
-        <v>94</v>
-      </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B13" s="2">
         <v>10105</v>
       </c>
@@ -1698,11 +1642,8 @@
       <c r="W13" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="X13" s="17" t="s">
-        <v>94</v>
-      </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B14" s="2">
         <v>10106</v>
       </c>
@@ -1749,11 +1690,8 @@
       <c r="W14" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="X14" s="17" t="s">
-        <v>94</v>
-      </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B15" s="2">
         <v>10107</v>
       </c>
@@ -1800,11 +1738,8 @@
       <c r="W15" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="X15" s="17" t="s">
-        <v>94</v>
-      </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.3">
       <c r="B16" s="2">
         <v>10108</v>
       </c>
@@ -1851,11 +1786,8 @@
       <c r="W16" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="X16" s="17" t="s">
-        <v>94</v>
-      </c>
     </row>
-    <row r="17" spans="2:24" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B17" s="2">
         <v>10109</v>
       </c>
@@ -1901,9 +1833,6 @@
       </c>
       <c r="W17" s="12" t="s">
         <v>68</v>
-      </c>
-      <c r="X17" s="17" t="s">
-        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/DialogueData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/DialogueData.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAE5D7CA-47C5-4ED8-B62B-E7AC8C432D7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView xWindow="0" yWindow="4840" windowWidth="42470" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="对话表" sheetId="1" r:id="rId1"/>
@@ -26,55 +32,8 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>tc={9638FB6C-ABC7-4DEB-BA79-91F240B16515}</author>
-    <author>tc={0F5F2D1B-07B1-4778-98B7-6F665943CEF5}</author>
-  </authors>
-  <commentList>
-    <comment ref="V2" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">[线程批注]
-你的Excel版本可读取此线程批注; 但如果在更新版本的Excel中打开文件，则对批注所作的任何改动都将被删除。了解详细信息: https://go.microsoft.com/fwlink/?linkid=870924
-注释:
-    Left	左
-Crent	中
-Right	右
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="W2" authorId="1">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">[线程批注]
-你的Excel版本可读取此线程批注; 但如果在更新版本的Excel中打开文件，则对批注所作的任何改动都将被删除。了解详细信息: https://go.microsoft.com/fwlink/?linkid=870924
-注释:
-    DEL	删除
-MASK	遮罩
-OVERRIDE	同时展示
-</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="77">
   <si>
     <t>##var</t>
   </si>
@@ -302,19 +261,17 @@
   </si>
   <si>
     <t>我的头啊</t>
+  </si>
+  <si>
+    <t>DramaDialogue+10100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -323,156 +280,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="9"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -491,194 +314,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -686,312 +323,27 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1249,41 +601,39 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="8.66666666666667"/>
     <col min="3" max="3" width="41.5" customWidth="1"/>
-    <col min="4" max="4" width="16.1666666666667" customWidth="1"/>
+    <col min="4" max="4" width="16.1640625" customWidth="1"/>
     <col min="5" max="5" width="19.75" customWidth="1"/>
-    <col min="6" max="6" width="23.4166666666667" customWidth="1"/>
+    <col min="6" max="6" width="23.4140625" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="43.3333333333333" customWidth="1"/>
+    <col min="8" max="8" width="43.33203125" customWidth="1"/>
     <col min="9" max="9" width="19.75" customWidth="1"/>
-    <col min="10" max="10" width="19.5833333333333" customWidth="1"/>
+    <col min="10" max="10" width="19.58203125" customWidth="1"/>
     <col min="11" max="11" width="23" customWidth="1"/>
     <col min="12" max="12" width="23.75" customWidth="1"/>
-    <col min="13" max="13" width="24.3333333333333" customWidth="1"/>
+    <col min="13" max="13" width="24.33203125" customWidth="1"/>
     <col min="14" max="14" width="18.5" customWidth="1"/>
-    <col min="15" max="15" width="17.0833333333333" customWidth="1"/>
-    <col min="16" max="16" width="15.9166666666667" customWidth="1"/>
-    <col min="17" max="17" width="17.1666666666667" customWidth="1"/>
-    <col min="18" max="18" width="16.4166666666667" customWidth="1"/>
-    <col min="19" max="19" width="13.3333333333333" customWidth="1"/>
-    <col min="20" max="20" width="13.4166666666667" customWidth="1"/>
-    <col min="21" max="21" width="17.0833333333333" customWidth="1"/>
+    <col min="15" max="15" width="17.08203125" customWidth="1"/>
+    <col min="16" max="16" width="15.9140625" customWidth="1"/>
+    <col min="17" max="17" width="17.1640625" customWidth="1"/>
+    <col min="18" max="18" width="16.4140625" customWidth="1"/>
+    <col min="19" max="19" width="13.33203125" customWidth="1"/>
+    <col min="20" max="20" width="13.4140625" customWidth="1"/>
+    <col min="21" max="21" width="17.08203125" customWidth="1"/>
     <col min="22" max="22" width="20" customWidth="1"/>
-    <col min="23" max="23" width="25.9166666666667" customWidth="1"/>
-    <col min="24" max="16384" width="8.66666666666667"/>
+    <col min="23" max="23" width="25.9140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1354,7 +704,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -1425,7 +775,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:23">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>34</v>
       </c>
@@ -1496,7 +846,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:23">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="1">
         <v>10000</v>
@@ -1517,7 +867,7 @@
         <v>58</v>
       </c>
       <c r="H4" s="1" t="str">
-        <f t="shared" ref="H4:H17" si="0">CONCATENATE("DramaDialogue+",B4)</f>
+        <f>CONCATENATE("DramaDialogue+",B4)</f>
         <v>DramaDialogue+10000</v>
       </c>
       <c r="I4" s="1">
@@ -1552,7 +902,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:23">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>10001</v>
@@ -1573,7 +923,7 @@
         <v>58</v>
       </c>
       <c r="H5" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="H5:H17" si="0">CONCATENATE("DramaDialogue+",B5)</f>
         <v>DramaDialogue+10001</v>
       </c>
       <c r="I5" s="1">
@@ -1610,7 +960,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:23">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>10002</v>
@@ -1668,7 +1018,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:23">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>10003</v>
@@ -1726,7 +1076,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:23">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
       <c r="B8" s="2">
         <v>10100</v>
@@ -1746,9 +1096,8 @@
       <c r="G8" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="H8" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>DramaDialogue+10100</v>
+      <c r="H8" s="3" t="s">
+        <v>76</v>
       </c>
       <c r="I8" s="2">
         <v>10101</v>
@@ -1782,7 +1131,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:23">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
       <c r="B9" s="2">
         <v>10101</v>
@@ -1840,7 +1189,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:23">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
       <c r="B10" s="2">
         <v>10102</v>
@@ -1898,7 +1247,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:23">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
       <c r="B11" s="2">
         <v>10103</v>
@@ -1958,7 +1307,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:23">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
       <c r="B12" s="2">
         <v>10104</v>
@@ -2014,7 +1363,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:23">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
       <c r="B13" s="2">
         <v>10105</v>
@@ -2070,7 +1419,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:23">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
       <c r="B14" s="2">
         <v>10106</v>
@@ -2126,7 +1475,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="1:23">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A15" s="2"/>
       <c r="B15" s="2">
         <v>10107</v>
@@ -2182,7 +1531,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="1:23">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
       <c r="B16" s="2">
         <v>10108</v>
@@ -2238,7 +1587,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="1:23">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A17" s="2"/>
       <c r="B17" s="2">
         <v>10109</v>
@@ -2295,9 +1644,8 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/DialogueData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/DialogueData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAE5D7CA-47C5-4ED8-B62B-E7AC8C432D7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F31200A1-8C8D-44AB-A97B-A427427FE96E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="4840" windowWidth="42470" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15070" yWindow="7470" windowWidth="42470" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="对话表" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="82">
   <si>
     <t>##var</t>
   </si>
@@ -264,6 +264,26 @@
   </si>
   <si>
     <t>DramaDialogue+10100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DramaDialogue+10000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DramaDialogue+10001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DramaDialogue+10002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DramaDialogue+10003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DramaDialogue+10101</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -327,11 +347,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -618,7 +649,7 @@
     <col min="8" max="8" width="43.33203125" customWidth="1"/>
     <col min="9" max="9" width="19.75" customWidth="1"/>
     <col min="10" max="10" width="19.58203125" customWidth="1"/>
-    <col min="11" max="11" width="23" customWidth="1"/>
+    <col min="11" max="11" width="23" style="6" customWidth="1"/>
     <col min="12" max="12" width="23.75" customWidth="1"/>
     <col min="13" max="13" width="24.33203125" customWidth="1"/>
     <col min="14" max="14" width="18.5" customWidth="1"/>
@@ -664,7 +695,7 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="6" t="s">
         <v>10</v>
       </c>
       <c r="L1" t="s">
@@ -735,7 +766,7 @@
       <c r="J2" t="s">
         <v>28</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="6" t="s">
         <v>28</v>
       </c>
       <c r="L2" t="s">
@@ -806,7 +837,7 @@
       <c r="J3" t="s">
         <v>43</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="6" t="s">
         <v>44</v>
       </c>
       <c r="L3" t="s">
@@ -866,15 +897,14 @@
       <c r="G4" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="H4" s="1" t="str">
-        <f>CONCATENATE("DramaDialogue+",B4)</f>
-        <v>DramaDialogue+10000</v>
+      <c r="H4" s="4" t="s">
+        <v>77</v>
       </c>
       <c r="I4" s="1">
         <v>10001</v>
       </c>
       <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
+      <c r="K4" s="7"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
       <c r="N4" s="1" t="s">
@@ -922,15 +952,14 @@
       <c r="G5" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="H5" s="1" t="str">
-        <f t="shared" ref="H5:H17" si="0">CONCATENATE("DramaDialogue+",B5)</f>
-        <v>DramaDialogue+10001</v>
+      <c r="H5" s="4" t="s">
+        <v>78</v>
       </c>
       <c r="I5" s="1">
         <v>10002</v>
       </c>
       <c r="J5" s="1"/>
-      <c r="K5" s="1">
+      <c r="K5" s="7">
         <v>10000</v>
       </c>
       <c r="L5" s="1"/>
@@ -980,15 +1009,14 @@
       <c r="G6" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="H6" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>DramaDialogue+10002</v>
+      <c r="H6" s="4" t="s">
+        <v>79</v>
       </c>
       <c r="I6" s="1">
         <v>10003</v>
       </c>
       <c r="J6" s="1"/>
-      <c r="K6" s="1">
+      <c r="K6" s="7">
         <v>10001</v>
       </c>
       <c r="L6" s="1"/>
@@ -1038,15 +1066,14 @@
       <c r="G7" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="H7" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>DramaDialogue+10003</v>
+      <c r="H7" s="4" t="s">
+        <v>80</v>
       </c>
       <c r="I7" s="1">
         <v>-1</v>
       </c>
       <c r="J7" s="1"/>
-      <c r="K7" s="1">
+      <c r="K7" s="7">
         <v>10002</v>
       </c>
       <c r="L7" s="1"/>
@@ -1103,7 +1130,7 @@
         <v>10101</v>
       </c>
       <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
+      <c r="K8" s="8"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2" t="s">
@@ -1151,15 +1178,14 @@
       <c r="G9" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="H9" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>DramaDialogue+10101</v>
+      <c r="H9" s="5" t="s">
+        <v>81</v>
       </c>
       <c r="I9" s="2">
         <v>10102</v>
       </c>
       <c r="J9" s="2"/>
-      <c r="K9" s="2">
+      <c r="K9" s="8">
         <v>10100</v>
       </c>
       <c r="L9" s="2"/>
@@ -1210,14 +1236,14 @@
         <v>58</v>
       </c>
       <c r="H10" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="H10:H17" si="0">CONCATENATE("DramaDialogue+",B10)</f>
         <v>DramaDialogue+10102</v>
       </c>
       <c r="I10" s="2">
         <v>10103</v>
       </c>
       <c r="J10" s="2"/>
-      <c r="K10" s="2">
+      <c r="K10" s="8">
         <v>10101</v>
       </c>
       <c r="L10" s="2"/>
@@ -1277,7 +1303,7 @@
       <c r="J11" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="K11" s="2">
+      <c r="K11" s="8">
         <v>10102</v>
       </c>
       <c r="L11" s="2"/>
@@ -1335,7 +1361,7 @@
         <v>10105</v>
       </c>
       <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
+      <c r="K12" s="8"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
       <c r="N12" s="2" t="s">
@@ -1391,7 +1417,7 @@
         <v>-1</v>
       </c>
       <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
+      <c r="K13" s="8"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
       <c r="N13" s="2" t="s">
@@ -1447,7 +1473,7 @@
         <v>10107</v>
       </c>
       <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
+      <c r="K14" s="8"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
       <c r="N14" s="2" t="s">
@@ -1503,7 +1529,7 @@
         <v>-1</v>
       </c>
       <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
+      <c r="K15" s="8"/>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
       <c r="N15" s="2" t="s">
@@ -1559,7 +1585,7 @@
         <v>10109</v>
       </c>
       <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
+      <c r="K16" s="8"/>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
       <c r="N16" s="2" t="s">
@@ -1615,7 +1641,7 @@
         <v>-1</v>
       </c>
       <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
+      <c r="K17" s="8"/>
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
       <c r="N17" s="2" t="s">

--- a/ExcelTool/LubanTools/DataTables/Datas/DialogueData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/DialogueData.xlsx
@@ -5,35 +5,22 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\Project\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F31200A1-8C8D-44AB-A97B-A427427FE96E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF4D978A-6D5A-4004-A6DF-C80C7DB4F73B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15070" yWindow="7470" windowWidth="42470" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7930" yWindow="5960" windowWidth="28800" windowHeight="14360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="对话表" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="88">
   <si>
     <t>##var</t>
   </si>
@@ -285,6 +272,24 @@
   <si>
     <t>DramaDialogue+10101</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>催稿-马吉回工作室-我知道了</t>
+  </si>
+  <si>
+    <t>MachiRoom+MachiRoom/RushCallLine1</t>
+  </si>
+  <si>
+    <t>催稿-马吉回工作室-好的啦</t>
+  </si>
+  <si>
+    <t>MachiRoom+MachiRoom/RushCallLine2</t>
+  </si>
+  <si>
+    <t>催稿-马吉回工作室-真讨厌</t>
+  </si>
+  <si>
+    <t>MachiRoom+MachiRoom/RushCallLine3</t>
   </si>
 </sst>
 </file>
@@ -347,7 +352,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -363,6 +368,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -638,7 +644,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W17"/>
+  <dimension ref="A1:W20"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="41.5" customWidth="1"/>
@@ -1669,6 +1675,147 @@
         <v>61</v>
       </c>
     </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B18">
+        <v>10200</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="D18">
+        <v>-1</v>
+      </c>
+      <c r="E18">
+        <v>-1</v>
+      </c>
+      <c r="F18">
+        <v>10005</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="I18">
+        <v>-1</v>
+      </c>
+      <c r="N18" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="O18" t="b">
+        <v>1</v>
+      </c>
+      <c r="P18" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>3</v>
+      </c>
+      <c r="U18">
+        <v>1</v>
+      </c>
+      <c r="V18" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="W18" s="9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B19">
+        <v>10201</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="D19">
+        <v>-1</v>
+      </c>
+      <c r="E19">
+        <v>-1</v>
+      </c>
+      <c r="F19">
+        <v>10005</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="I19">
+        <v>-1</v>
+      </c>
+      <c r="N19" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="O19" t="b">
+        <v>1</v>
+      </c>
+      <c r="P19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>3</v>
+      </c>
+      <c r="U19">
+        <v>1</v>
+      </c>
+      <c r="V19" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="W19" s="9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="B20">
+        <v>10202</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="D20">
+        <v>-1</v>
+      </c>
+      <c r="E20">
+        <v>-1</v>
+      </c>
+      <c r="F20">
+        <v>10005</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="I20">
+        <v>-1</v>
+      </c>
+      <c r="N20" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="O20" t="b">
+        <v>1</v>
+      </c>
+      <c r="P20" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>3</v>
+      </c>
+      <c r="U20">
+        <v>1</v>
+      </c>
+      <c r="V20" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="W20" s="9" t="s">
+        <v>61</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
